--- a/artfynd/A 9205-2026 artfynd.xlsx
+++ b/artfynd/A 9205-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121434116</v>
+        <v>120181138</v>
       </c>
       <c r="B2" t="n">
-        <v>90110</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640364</v>
+        <v>640388</v>
       </c>
       <c r="R2" t="n">
-        <v>6555420</v>
+        <v>6555348</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,27 +742,27 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ytterjärna</t>
+          <t>Överjärna</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,22 +771,357 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121434116</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91282</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>640364</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6555420</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ytterjärna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121554375</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>640143</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6555629</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterjärna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121433794</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>640379</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6555397</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9205-2026 artfynd.xlsx
+++ b/artfynd/A 9205-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120181138</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121434116</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121554375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,8 +1142,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121433794</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>